--- a/Assets/Config/Excel/UISprite.xlsx
+++ b/Assets/Config/Excel/UISprite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -601,6 +601,512 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sheep_1001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SheepIcon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SheepIcon1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>羊咩咩(羊图鉴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sheep_1002</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SheepIcon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SheepIcon2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>卷卷(羊图鉴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sheep_1003</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SheepIcon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SheepIcon3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>奶茶(羊图鉴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sheep_1004</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SheepIcon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SheepIcon4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>雪球(羊图鉴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>brick_bell</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BrickBell</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>brick_bonfire</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BrickBonfire</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>brick_bottle</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BrickBottle</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>brick_brush</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BrickBrush</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>brick_bucket</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BrickBucket</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>brick_cabbage</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BrickCabbage</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>brick_carrot</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BrickCarrot</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>brick_corn</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BrickCorn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>brick_fok</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BrickFok</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>brick_glove</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BrickGlove</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>brick_grass</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BrickGrass</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>brick_scissors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BricksCissors</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>brick_straw</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BrickStraw</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>brick_wood</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BrickWood</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>brick_wool</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BrickWool</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>brick_yarn</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BrickYarn</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>砖块图鉴</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ui_red_dot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>红点</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>icon_coin</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CoinIcon</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>金币图标</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>icon_diamond</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DiamondIcon</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>钻石图标</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
